--- a/questionnaire_templates/013_personal_narrative_writing_guide--questionnaire_templates.xlsx
+++ b/questionnaire_templates/013_personal_narrative_writing_guide--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>personal_narrative_writing_guide</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Personal Narrative Writing Guide</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Form Category</t>
+          <t>Form Category2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Form Description</t>
+          <t>Form Description2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Form Title</t>
+          <t>Form Title2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Form Description</t>
+          <t>Form Description3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,16 +865,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>form_title3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Form Title3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -894,9 +917,9 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'questionnaire_templates'}</t>
+          <t>questionnaire_templates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Questionnaire Templates'}</t>
+          <t>Questionnaire Templates</t>
         </is>
       </c>
     </row>
@@ -941,46 +964,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'form_templates'}</t>
+          <t>form_templates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Form Templates'}</t>
+          <t>Form Templates</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'questionnaire_templates'}</t>
+          <t>questionnaire_templates</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Questionnaire Templates'}</t>
+          <t>Questionnaire Templates</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'form_templates'}</t>
+          <t>form_templates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Form Templates'}</t>
+          <t>Form Templates</t>
         </is>
       </c>
     </row>
